--- a/Result/profitability/3023.xlsx
+++ b/Result/profitability/3023.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>2.98375</v>
+        <v>2.96</v>
       </c>
       <c r="N2" t="n">
-        <v>23.29625</v>
+        <v>23.34125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.11</v>
       </c>
       <c r="M3" t="n">
-        <v>2.50375</v>
+        <v>2.5925</v>
       </c>
       <c r="N3" t="n">
-        <v>22.19375</v>
+        <v>22.25375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.64</v>
       </c>
       <c r="M4" t="n">
-        <v>2.2025</v>
+        <v>2.19125</v>
       </c>
       <c r="N4" t="n">
-        <v>21.04125</v>
+        <v>21.045</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.99</v>
       </c>
       <c r="M5" t="n">
-        <v>1.5975</v>
+        <v>1.6725</v>
       </c>
       <c r="N5" t="n">
-        <v>20.27</v>
+        <v>20.24875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2525</v>
+        <v>1.34125</v>
       </c>
       <c r="N6" t="n">
-        <v>19.5975</v>
+        <v>19.7875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.58</v>
       </c>
       <c r="M7" t="n">
-        <v>0.94375</v>
+        <v>1.04375</v>
       </c>
       <c r="N7" t="n">
-        <v>19.2625</v>
+        <v>19.375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="N8" t="n">
-        <v>19.03125</v>
+        <v>19.035</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3023</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9019</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6805</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2213</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="G75" t="n">
+        <v>939</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.41%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>150</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1089</v>
+      </c>
+      <c r="K75" t="n">
+        <v>903</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.4225</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.14625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1599999999999997</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.04444444444444429</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.02999999999999758</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.001223990208078174</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.5999999999999996</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.1898734177215189</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.1700000000000017</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.00687980574666136</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
